--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1906-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1906-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09A6686B-1427-4A83-8A7C-ABE9679DE87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37BCD7D0-CDD8-4E95-B0F3-F9BCA46E42F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FC0F4D85-0EC4-49C0-AA80-0D2B0FDEF46D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{301D653A-1EA2-4BFB-BB6A-7D2D5BAEB877}"/>
   </bookViews>
   <sheets>
     <sheet name="1906-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,20 +1490,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06341C42-C41D-4246-AA82-46EEECFC40F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BB3F71-E8D9-41E6-A4BF-2DB6278ACC2F}">
   <dimension ref="A1:R62"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1657,7 +1657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2024</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>2023</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2022</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2021</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2020</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2019</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2018</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2017</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2016</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2015</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2014</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2013</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2012</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2011</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2010</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2009</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2008</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2007</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>2006</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>2005</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>2004</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>2003</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>2002</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>2001</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>2000</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="40">
         <v>1999</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>1998</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="40">
         <v>1997</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="38">
         <v>1996</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
         <v>1995</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="38">
         <v>1994</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="40">
         <v>1993</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="38">
         <v>1992</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="40">
         <v>1991</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="38">
         <v>1990</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="40" t="s">
         <v>48</v>
       </c>
